--- a/ZonasEscolares/excels/LIMA-LIMA-LURIGANCHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LURIGANCHO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-LURIGANCHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LURIGANCHO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>JESUS DE NAZARETH - BELEN</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.98622</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.93539</v>
-      </c>
-      <c r="I2" t="n">
-        <v>249</v>
-      </c>
-      <c r="J2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.98622</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.93539</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>1267</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.98169</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.91517</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1493</v>
-      </c>
-      <c r="J3" t="n">
-        <v>63</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.98169</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.91517</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1493</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>105</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.98381</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.94132999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>420</v>
-      </c>
-      <c r="J4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.98381</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.94133</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>1275</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.9717</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.8961</v>
-      </c>
-      <c r="I5" t="n">
-        <v>504</v>
-      </c>
-      <c r="J5" t="n">
-        <v>20</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.9717</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.8961</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>COLEGIO EXPERIMENTAL DE APLICACION DE LA UNE ENRIQUE GUZMAN Y VALLE</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.94414</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.69895</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1310</v>
-      </c>
-      <c r="J6" t="n">
-        <v>83</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.94414</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.69895</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>200 LOS ANGELITOS DEL SABER</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.0014</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.8835</v>
-      </c>
-      <c r="I7" t="n">
-        <v>174</v>
-      </c>
-      <c r="J7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.0014</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.8835</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>0055 MANUEL GONZALES PRADA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.93982</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.71178999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>691</v>
-      </c>
-      <c r="J8" t="n">
-        <v>36</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.93982</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.71179</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>0059 SANTA MARIA GORETTI</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.98143</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.82186</v>
-      </c>
-      <c r="I9" t="n">
-        <v>965</v>
-      </c>
-      <c r="J9" t="n">
-        <v>35</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.98143</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.82186</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>0033 VIRGILIO ESPINOZA BARRIOS</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.01372</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.91828</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1139</v>
-      </c>
-      <c r="J10" t="n">
-        <v>51</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.01372</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.91828</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>1190 FELIPE HUAMAN POMA DE AYALA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.92475</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.68553</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1444</v>
-      </c>
-      <c r="J11" t="n">
-        <v>83</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.92475</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.68553</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>0065 MARISCAL ANDRES A. CACERES</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.9336</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.70291</v>
-      </c>
-      <c r="I12" t="n">
-        <v>333</v>
-      </c>
-      <c r="J12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.9336</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.70291</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>1282 AYMON LA CRUZ LOPEZ</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.00228</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.92308</v>
-      </c>
-      <c r="I13" t="n">
-        <v>689</v>
-      </c>
-      <c r="J13" t="n">
-        <v>24</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.00228</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.92308</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>1206 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.94819</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.7298</v>
-      </c>
-      <c r="I14" t="n">
-        <v>336</v>
-      </c>
-      <c r="J14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.94819</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.7298</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>0027 SAN ANTONIO JICAMARCA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.98417</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.94085</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2487</v>
-      </c>
-      <c r="J15" t="n">
-        <v>95</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.98417</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.94085</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>1234 / 1234 ROSA SANTANA PISCONTE</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.93427</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.71576</v>
-      </c>
-      <c r="I16" t="n">
-        <v>249</v>
-      </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.93427</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.71576</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>110</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.0192</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.91942</v>
-      </c>
-      <c r="I17" t="n">
-        <v>287</v>
-      </c>
-      <c r="J17" t="n">
-        <v>13</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.0192</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.91942</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>128 SANTA ROSITA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.98153</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.82217</v>
-      </c>
-      <c r="I18" t="n">
-        <v>203</v>
-      </c>
-      <c r="J18" t="n">
-        <v>9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.98153</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.82217</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>1195 CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.94207</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.69933</v>
-      </c>
-      <c r="I19" t="n">
-        <v>334</v>
-      </c>
-      <c r="J19" t="n">
-        <v>19</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.94207</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.69933</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>1224</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.9964</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.9226</v>
-      </c>
-      <c r="I20" t="n">
-        <v>872</v>
-      </c>
-      <c r="J20" t="n">
-        <v>34</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.9964</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.9226</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>161</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.99909</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.86713</v>
-      </c>
-      <c r="I21" t="n">
-        <v>213</v>
-      </c>
-      <c r="J21" t="n">
-        <v>11</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.99909</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.86713</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>1250</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.99723</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.91195999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>333</v>
-      </c>
-      <c r="J22" t="n">
-        <v>16</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.99723</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.91196</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>1194</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.93454</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.69095</v>
-      </c>
-      <c r="I23" t="n">
-        <v>308</v>
-      </c>
-      <c r="J23" t="n">
-        <v>14</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.93454</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.69095</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>0058 CUSCO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.92888</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.69056</v>
-      </c>
-      <c r="I24" t="n">
-        <v>659</v>
-      </c>
-      <c r="J24" t="n">
-        <v>29</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.92888</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.69056</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>0063 LETICIA KIEFFER MARCHAND</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.93872</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.69901</v>
-      </c>
-      <c r="I25" t="n">
-        <v>283</v>
-      </c>
-      <c r="J25" t="n">
-        <v>14</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.93872</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.69901</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>1198 LA RIBERA</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.94326</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.70347</v>
-      </c>
-      <c r="I26" t="n">
-        <v>529</v>
-      </c>
-      <c r="J26" t="n">
-        <v>31</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.94326</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.70347</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>1197 NICOLAS DE PIEROLA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-11.94393</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.71214999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>214</v>
-      </c>
-      <c r="J27" t="n">
-        <v>9</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-11.94393</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.71215</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>1200 SANTA MARIA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-11.948573</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.716791</v>
-      </c>
-      <c r="I28" t="n">
-        <v>362</v>
-      </c>
-      <c r="J28" t="n">
-        <v>19</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-11.948573</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.716791</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>1205 ABELARDO QUIÑONES</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-11.99263</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.91755999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>265</v>
-      </c>
-      <c r="J29" t="n">
-        <v>8</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-11.99263</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.91756</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>0051 JOSE F. SANCHEZ CARRION</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-11.99946</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.86647000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1805</v>
-      </c>
-      <c r="J30" t="n">
-        <v>81</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-11.99946</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.86647</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>PABLO PATRON</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-11.92764</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.68543</v>
-      </c>
-      <c r="I31" t="n">
-        <v>550</v>
-      </c>
-      <c r="J31" t="n">
-        <v>40</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-11.92764</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.68543</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>1233 MANUEL FERNANDO CABREL NICHO</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-11.9868</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.8989</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1816</v>
-      </c>
-      <c r="J32" t="n">
-        <v>71</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-11.9868</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.8989</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1816</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>JOSEFA CARRILLO Y ALBORNOZ</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-11.92845</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.68631000000001</v>
-      </c>
-      <c r="I33" t="n">
-        <v>541</v>
-      </c>
-      <c r="J33" t="n">
-        <v>39</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-11.92845</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.68631</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>1276</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-11.98006</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.90824000000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>345</v>
-      </c>
-      <c r="J34" t="n">
-        <v>13</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-11.98006</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.90824</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>1223</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.00154</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.93246000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>351</v>
-      </c>
-      <c r="J35" t="n">
-        <v>13</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.00154</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.93246</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>1277 DIVINO SALVADOR</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-11.9848</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.9486</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1010</v>
-      </c>
-      <c r="J36" t="n">
-        <v>43</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-11.9848</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.9486</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>FOYER SANTA ROSA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-11.97814</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.81153999999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>598</v>
-      </c>
-      <c r="J37" t="n">
-        <v>39</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-11.97814</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.81154</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.01796</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.94701999999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>187</v>
-      </c>
-      <c r="J38" t="n">
-        <v>5</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.01796</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.94702</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>FE Y ALEGRIA 41</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-11.98122</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.83804000000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1127</v>
-      </c>
-      <c r="J39" t="n">
-        <v>47</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-11.98122</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.83804</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>LA ROCA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-11.94218</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.70663</v>
-      </c>
-      <c r="I40" t="n">
-        <v>232</v>
-      </c>
-      <c r="J40" t="n">
-        <v>38</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-11.94218</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.70663</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>MI JESUS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-11.98328</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.83671</v>
-      </c>
-      <c r="I41" t="n">
-        <v>284</v>
-      </c>
-      <c r="J41" t="n">
-        <v>18</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-11.98328</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.83671</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>NUESTRA SEÑORA DE LA SABIDURIA</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-11.9798</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.81999999999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>802</v>
-      </c>
-      <c r="J42" t="n">
-        <v>44</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-11.9798</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.82</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>SAN ISIDRO</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-11.93699</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.69467</v>
-      </c>
-      <c r="I43" t="n">
-        <v>211</v>
-      </c>
-      <c r="J43" t="n">
-        <v>7</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-11.93699</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.69467</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>SAN IISIDRO PATRON DE JICAMARCA / SAN ISIDRO PATRON DE JICAMARCA</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-11.97697</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.94271999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>574</v>
-      </c>
-      <c r="J44" t="n">
-        <v>28</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-11.97697</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.94272</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>SANTA ROSA</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-11.93658</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.69814</v>
-      </c>
-      <c r="I45" t="n">
-        <v>491</v>
-      </c>
-      <c r="J45" t="n">
-        <v>42</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-11.93658</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.69814</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>UNION</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-11.98809</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-76.83953</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1356</v>
-      </c>
-      <c r="J46" t="n">
-        <v>71</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-11.98809</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-76.83953</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-11.93823</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-76.69913</v>
-      </c>
-      <c r="I47" t="n">
-        <v>256</v>
-      </c>
-      <c r="J47" t="n">
-        <v>20</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-11.93823</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-76.69913</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>DEUNI</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-11.9445</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-76.71089000000001</v>
-      </c>
-      <c r="I48" t="n">
-        <v>261</v>
-      </c>
-      <c r="J48" t="n">
-        <v>26</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-11.9445</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-76.71089</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>EMANUEL</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.00365</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-76.92243000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>372</v>
-      </c>
-      <c r="J49" t="n">
-        <v>19</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.00365</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-76.92243</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>20955-2 NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-11.979292</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-76.91076099999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1713</v>
-      </c>
-      <c r="J50" t="n">
-        <v>75</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-11.979292</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-76.910761</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>20955-14 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.006905</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-76.956233</v>
-      </c>
-      <c r="I51" t="n">
-        <v>677</v>
-      </c>
-      <c r="J51" t="n">
-        <v>41</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.006905</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-76.956233</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>20955-17</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-11.985551</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-76.91899100000001</v>
-      </c>
-      <c r="I52" t="n">
-        <v>339</v>
-      </c>
-      <c r="J52" t="n">
-        <v>18</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-11.985551</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-76.918991</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>20955-18 JERUSALEN</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-11.980042</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-76.831598</v>
-      </c>
-      <c r="I53" t="n">
-        <v>202</v>
-      </c>
-      <c r="J53" t="n">
-        <v>10</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-11.980042</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-76.831598</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>CRISTO DE LA PAZ DE CAJAMARQUILLA</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-11.979027</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-76.908502</v>
-      </c>
-      <c r="I54" t="n">
-        <v>205</v>
-      </c>
-      <c r="J54" t="n">
-        <v>20</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-11.979027</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-76.908502</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>20955-15</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-11.98342</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-76.929394</v>
-      </c>
-      <c r="I55" t="n">
-        <v>786</v>
-      </c>
-      <c r="J55" t="n">
-        <v>44</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-11.98342</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-76.929394</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>PADRE MIGUEL MARINA</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-11.9936</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-76.9545</v>
-      </c>
-      <c r="I56" t="n">
-        <v>337</v>
-      </c>
-      <c r="J56" t="n">
-        <v>12</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-11.9936</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-76.9545</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>WILLIAM SHAKESPEARE DE CARAPONGO</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-12.00502</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-76.87542999999999</v>
-      </c>
-      <c r="I57" t="n">
-        <v>320</v>
-      </c>
-      <c r="J57" t="n">
-        <v>26</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-12.00502</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-76.87543</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>INMACULADA CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-11.97685</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-76.9405</v>
-      </c>
-      <c r="I58" t="n">
-        <v>242</v>
-      </c>
-      <c r="J58" t="n">
-        <v>10</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-11.97685</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-76.9405</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>1197 NICOLAS DE PIEROLA</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-11.94396</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-76.7122</v>
-      </c>
-      <c r="I59" t="n">
-        <v>315</v>
-      </c>
-      <c r="J59" t="n">
-        <v>21</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-11.94396</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-76.7122</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>COAR ARTISTICO DE LIMA / COLEGIO MAYOR SECUNDARIO PRESIDENTE DEL PERU</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-11.973926</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-76.77386199999999</v>
-      </c>
-      <c r="I60" t="n">
-        <v>886</v>
-      </c>
-      <c r="J60" t="n">
-        <v>75</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-11.973926</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-76.773862</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>LA CATOLICA DE CARAPONGO</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-12.00418</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-76.87394999999999</v>
-      </c>
-      <c r="I61" t="n">
-        <v>389</v>
-      </c>
-      <c r="J61" t="n">
-        <v>24</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-12.00418</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-76.87395</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>KOREB SCHOOL</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-12.00595</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-76.87465</v>
-      </c>
-      <c r="I62" t="n">
-        <v>335</v>
-      </c>
-      <c r="J62" t="n">
-        <v>23</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-12.00595</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-76.87465</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>ANTONIO RAIMONDI</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-11.98814</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-76.83947000000001</v>
-      </c>
-      <c r="I63" t="n">
-        <v>253</v>
-      </c>
-      <c r="J63" t="n">
-        <v>14</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-11.98814</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-76.83947</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>NUEVO MUNDO</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-11.96099</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-76.73793999999999</v>
-      </c>
-      <c r="I64" t="n">
-        <v>294</v>
-      </c>
-      <c r="J64" t="n">
-        <v>19</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-11.96099</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-76.73794</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>CORAZON DE JESUS DE JICAMARCA</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-11.98225</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-76.934313</v>
-      </c>
-      <c r="I65" t="n">
-        <v>527</v>
-      </c>
-      <c r="J65" t="n">
-        <v>32</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-11.98225</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-76.934313</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>0052 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-11.93779</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-76.69369</v>
-      </c>
-      <c r="I66" t="n">
-        <v>286</v>
-      </c>
-      <c r="J66" t="n">
-        <v>13</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-11.93779</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-76.69369</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>IDUKAY</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-11.93442</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-76.68984</v>
-      </c>
-      <c r="I67" t="n">
-        <v>25</v>
-      </c>
-      <c r="J67" t="n">
-        <v>3</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-11.93442</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-76.68984</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>SANTISIMA VIRGEN MARIA</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-11.9899</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-76.91624</v>
-      </c>
-      <c r="I68" t="n">
-        <v>335</v>
-      </c>
-      <c r="J68" t="n">
-        <v>15</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-11.9899</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-76.91624</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>PERUANO AMERICANO</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-12.0011</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-76.8771</v>
-      </c>
-      <c r="I69" t="n">
-        <v>735</v>
-      </c>
-      <c r="J69" t="n">
-        <v>45</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-12.0011</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-76.8771</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>ANGELITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-11.993336</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-76.904096</v>
-      </c>
-      <c r="I70" t="n">
-        <v>404</v>
-      </c>
-      <c r="J70" t="n">
-        <v>9</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-11.993336</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-76.904096</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>FE Y ALEGRIA 58 MARY WARD</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-11.969241</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-76.94247900000001</v>
-      </c>
-      <c r="I71" t="n">
-        <v>1089</v>
-      </c>
-      <c r="J71" t="n">
-        <v>52</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-11.969241</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-76.942479</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>WINNER SCHOOL</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-12.00382</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-76.92230000000001</v>
-      </c>
-      <c r="I72" t="n">
-        <v>429</v>
-      </c>
-      <c r="J72" t="n">
-        <v>30</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-12.00382</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-76.9223</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>CORAZON DE JESUS DE JICAMARCA</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-11.9821</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-76.9341</v>
-      </c>
-      <c r="I73" t="n">
-        <v>902</v>
-      </c>
-      <c r="J73" t="n">
-        <v>31</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-11.9821</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-76.9341</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>20955-26 INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-11.96624</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-76.79490199999999</v>
-      </c>
-      <c r="I74" t="n">
-        <v>316</v>
-      </c>
-      <c r="J74" t="n">
-        <v>21</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-11.96624</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-76.794902</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>KIDS &amp; KIDS</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-12.00564</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-76.92616</v>
-      </c>
-      <c r="I75" t="n">
-        <v>247</v>
-      </c>
-      <c r="J75" t="n">
-        <v>14</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-12.00564</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-76.92616</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>SAN PEDRO Y SAN PABLO</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-11.96605</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-76.93461000000001</v>
-      </c>
-      <c r="I76" t="n">
-        <v>366</v>
-      </c>
-      <c r="J76" t="n">
-        <v>12</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-11.96605</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-76.93461</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>SEMILLITAS DEL VALLECITO IV</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-11.97257</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-76.83882</v>
-      </c>
-      <c r="I77" t="n">
-        <v>263</v>
-      </c>
-      <c r="J77" t="n">
-        <v>9</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-11.97257</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-76.83882</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>INTERNATIONAL COLLEGE</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-11.97782</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-76.9387</v>
-      </c>
-      <c r="I78" t="n">
-        <v>224</v>
-      </c>
-      <c r="J78" t="n">
-        <v>3</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-11.97782</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-76.9387</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>FRANCOIS VIETE</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-12.001755</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-76.867586</v>
-      </c>
-      <c r="I79" t="n">
-        <v>187</v>
-      </c>
-      <c r="J79" t="n">
-        <v>5</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-12.001755</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-76.867586</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>LITTLE LION OF JUDAH</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-11.9877</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-76.93416999999999</v>
-      </c>
-      <c r="I80" t="n">
-        <v>238</v>
-      </c>
-      <c r="J80" t="n">
-        <v>16</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-11.9877</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-76.93417</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>REY SALOMON</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-11.97177</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-76.939611</v>
-      </c>
-      <c r="I81" t="n">
-        <v>222</v>
-      </c>
-      <c r="J81" t="n">
-        <v>14</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-11.97177</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-76.939611</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>SAN PEDRO Y SAN PABLO</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-11.96436</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-76.93428</v>
-      </c>
-      <c r="I82" t="n">
-        <v>253</v>
-      </c>
-      <c r="J82" t="n">
-        <v>10</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-11.96436</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-76.93428</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>CUSSI SCHOOL</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-12.002828</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-76.86747800000001</v>
-      </c>
-      <c r="I83" t="n">
-        <v>191</v>
-      </c>
-      <c r="J83" t="n">
-        <v>10</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-12.002828</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-76.867478</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>MONTESSORI DE CARAPONGO</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-11.936429</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-76.69670600000001</v>
-      </c>
-      <c r="I84" t="n">
-        <v>342</v>
-      </c>
-      <c r="J84" t="n">
-        <v>16</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-11.936429</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-76.696706</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>ADELISES I</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-11.994589</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-76.941857</v>
-      </c>
-      <c r="I85" t="n">
-        <v>234</v>
-      </c>
-      <c r="J85" t="n">
-        <v>12</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-11.994589</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-76.941857</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>SAINT GERARD SCHOOL</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-12.01429</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-76.93867</v>
-      </c>
-      <c r="I86" t="n">
-        <v>322</v>
-      </c>
-      <c r="J86" t="n">
-        <v>22</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-12.01429</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-76.93867</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>MASTER GENIO</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-11.982406</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-76.941773</v>
-      </c>
-      <c r="I87" t="n">
-        <v>200</v>
-      </c>
-      <c r="J87" t="n">
-        <v>18</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-11.982406</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-76.941773</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>EL NAZARENO DE JESUS</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-11.977326</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-76.937434</v>
-      </c>
-      <c r="I88" t="n">
-        <v>231</v>
-      </c>
-      <c r="J88" t="n">
-        <v>15</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-11.977326</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-76.937434</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>GOLEMAN SCHOOL</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-11.975162</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-76.94388600000001</v>
-      </c>
-      <c r="I89" t="n">
-        <v>316</v>
-      </c>
-      <c r="J89" t="n">
-        <v>14</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-11.975162</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-76.943886</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-LURIGANCHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LURIGANCHO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>104192</t>
+          <t>755895</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARETH - BELEN</t>
+          <t>LAS BRISAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.98622</t>
+          <t>-11.99875</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.93539</t>
+          <t>-76.92141</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>313591</t>
+          <t>655235</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>SAN IGNACIO DE ÑAÑA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.98169</t>
+          <t>-11.97709</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.91517</t>
+          <t>-76.80456</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>112</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>313628</t>
+          <t>655184</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.98381</t>
+          <t>-11.97568</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.94133</t>
+          <t>-76.791</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>163</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>313633</t>
+          <t>619488</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>LOS ALAMOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.9717</t>
+          <t>-11.98655</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.8961</t>
+          <t>-76.83315</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>186</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,42 +749,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>313652</t>
+          <t>313685</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COLEGIO EXPERIMENTAL DE APLICACION DE LA UNE ENRIQUE GUZMAN Y VALLE</t>
+          <t>200 LOS ANGELITOS DEL SABER</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.94414</t>
+          <t>-12.0014</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.69895</t>
+          <t>-76.8835</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>174</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,27 +811,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>313685</t>
+          <t>357815</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>200 LOS ANGELITOS DEL SABER</t>
+          <t>20955-18 JERUSALEN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.0014</t>
+          <t>-11.980042</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.8835</t>
+          <t>-76.831598</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>313708</t>
+          <t>539236</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0055 MANUEL GONZALES PRADA</t>
+          <t>INMACULADA CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.93982</t>
+          <t>-11.97685</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.71179</t>
+          <t>-76.9405</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>313713</t>
+          <t>823615</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0059 SANTA MARIA GORETTI</t>
+          <t>SAN PEDRO Y SAN PABLO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.98143</t>
+          <t>-11.96436</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.82186</t>
+          <t>-76.93428</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>253</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>313727</t>
+          <t>825600</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0033 VIRGILIO ESPINOZA BARRIOS</t>
+          <t>CUSSI SCHOOL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.01372</t>
+          <t>-12.002828</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.91828</t>
+          <t>-76.867478</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>191</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>313732</t>
+          <t>313954</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1190 FELIPE HUAMAN POMA DE AYALA</t>
+          <t>161</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.92475</t>
+          <t>-11.99909</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.68553</t>
+          <t>-76.86713</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>313765</t>
+          <t>517338</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0065 MARISCAL ANDRES A. CACERES</t>
+          <t>PADRE MIGUEL MARINA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.9336</t>
+          <t>-11.9936</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.70291</t>
+          <t>-76.9545</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>313789</t>
+          <t>780098</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1282 AYMON LA CRUZ LOPEZ</t>
+          <t>SAN PEDRO Y SAN PABLO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.00228</t>
+          <t>-11.96605</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.92308</t>
+          <t>-76.93461</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>366</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>313794</t>
+          <t>839046</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1206 DANIEL ALCIDES CARRION</t>
+          <t>ADELISES I</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.94819</t>
+          <t>-11.994589</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.7298</t>
+          <t>-76.941857</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,42 +1307,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>313845</t>
+          <t>313874</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0027 SAN ANTONIO JICAMARCA</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.98417</t>
+          <t>-12.0192</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.94085</t>
+          <t>-76.91942</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>287</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>313850</t>
+          <t>314246</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1234 / 1234 ROSA SANTANA PISCONTE</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.93427</t>
+          <t>-11.98006</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.71576</t>
+          <t>-76.90824</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>313874</t>
+          <t>314251</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.0192</t>
+          <t>-12.00154</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.91942</t>
+          <t>-76.93246</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>313888</t>
+          <t>718426</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>128 SANTA ROSITA</t>
+          <t>0052 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.98153</t>
+          <t>-11.93779</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.82217</t>
+          <t>-76.69369</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>286</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>313911</t>
+          <t>313850</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1195 CESAR VALLEJO</t>
+          <t>1234 / 1234 ROSA SANTANA PISCONTE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.94207</t>
+          <t>-11.93427</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.69933</t>
+          <t>-76.71576</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>313930</t>
+          <t>314034</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.9964</t>
+          <t>-11.93454</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.9226</t>
+          <t>-76.69095</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>313954</t>
+          <t>314053</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>0063 LETICIA KIEFFER MARCHAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.99909</t>
+          <t>-11.93872</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.86713</t>
+          <t>-76.69901</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>314005</t>
+          <t>619445</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.99723</t>
+          <t>-11.98814</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.91196</t>
+          <t>-76.83947</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>253</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,27 +1803,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>314034</t>
+          <t>751208</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>KIDS &amp; KIDS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.93454</t>
+          <t>-12.00564</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.69095</t>
+          <t>-76.92616</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>314048</t>
+          <t>814418</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0058 CUSCO</t>
+          <t>REY SALOMON</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.92888</t>
+          <t>-11.97177</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.69056</t>
+          <t>-76.939611</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>314053</t>
+          <t>901444</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0063 LETICIA KIEFFER MARCHAND</t>
+          <t>GOLEMAN SCHOOL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.93872</t>
+          <t>-11.975162</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.69901</t>
+          <t>-76.943886</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>316</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>314067</t>
+          <t>313794</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1198 LA RIBERA</t>
+          <t>1206 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.94326</t>
+          <t>-11.94819</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.70347</t>
+          <t>-76.7298</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>336</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>314086</t>
+          <t>720325</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1197 NICOLAS DE PIEROLA</t>
+          <t>SANTISIMA VIRGEN MARIA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.94393</t>
+          <t>-11.9899</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.71215</t>
+          <t>-76.91624</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>314114</t>
+          <t>857040</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1200 SANTA MARIA</t>
+          <t>EL NAZARENO DE JESUS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.948573</t>
+          <t>-11.977326</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.716791</t>
+          <t>-76.937434</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>314147</t>
+          <t>313628</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1205 ABELARDO QUIÑONES</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.99263</t>
+          <t>-11.98381</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.91756</t>
+          <t>-76.94133</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>420</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>314152</t>
+          <t>314005</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0051 JOSE F. SANCHEZ CARRION</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.99946</t>
+          <t>-11.99723</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.86647</t>
+          <t>-76.91196</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>314171</t>
+          <t>808059</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PABLO PATRON</t>
+          <t>LITTLE LION OF JUDAH</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.92764</t>
+          <t>-11.9877</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.68543</t>
+          <t>-76.93417</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>314213</t>
+          <t>835010</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1233 MANUEL FERNANDO CABREL NICHO</t>
+          <t>MONTESSORI DE CARAPONGO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.9868</t>
+          <t>-11.936429</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.8989</t>
+          <t>-76.696706</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>342</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>314227</t>
+          <t>314581</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JOSEFA CARRILLO Y ALBORNOZ</t>
+          <t>MI JESUS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.92845</t>
+          <t>-11.98328</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.68631</t>
+          <t>-76.83671</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>314246</t>
+          <t>357797</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>20955-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.98006</t>
+          <t>-11.985551</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.90824</t>
+          <t>-76.918991</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>339</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>314251</t>
+          <t>854616</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>MASTER GENIO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.00154</t>
+          <t>-11.982406</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.93246</t>
+          <t>-76.941773</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>314289</t>
+          <t>313911</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1277 DIVINO SALVADOR</t>
+          <t>1195 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.9848</t>
+          <t>-11.94207</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.9486</t>
+          <t>-76.69933</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>334</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>314345</t>
+          <t>314114</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FOYER SANTA ROSA</t>
+          <t>1200 SANTA MARIA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.97814</t>
+          <t>-11.948573</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.81154</t>
+          <t>-76.716791</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2733,42 +2733,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>314369</t>
+          <t>314821</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SANTA RITA DE CASIA</t>
+          <t>EMANUEL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.01796</t>
+          <t>-12.00365</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.94702</t>
+          <t>-76.92243</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>314519</t>
+          <t>651968</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 41</t>
+          <t>NUEVO MUNDO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.98122</t>
+          <t>-11.96099</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.83804</t>
+          <t>-76.73794</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>314576</t>
+          <t>313633</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LA ROCA</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.94218</t>
+          <t>-11.9717</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.70663</t>
+          <t>-76.8961</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>504</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>314581</t>
+          <t>313765</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MI JESUS</t>
+          <t>0065 MARISCAL ANDRES A. CACERES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.98328</t>
+          <t>-11.9336</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.83671</t>
+          <t>-76.70291</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>314604</t>
+          <t>314736</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA SABIDURIA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.9798</t>
+          <t>-11.93823</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.82</t>
+          <t>-76.69913</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>256</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>314637</t>
+          <t>357858</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>CRISTO DE LA PAZ DE CAJAMARQUILLA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.93699</t>
+          <t>-11.979027</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.69467</t>
+          <t>-76.908502</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>314661</t>
+          <t>539298</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SAN IISIDRO PATRON DE JICAMARCA / SAN ISIDRO PATRON DE JICAMARCA</t>
+          <t>1197 NICOLAS DE PIEROLA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.97697</t>
+          <t>-11.94396</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.94272</t>
+          <t>-76.7122</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>315</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>314680</t>
+          <t>737934</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>20955-26 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.93658</t>
+          <t>-11.96624</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.69814</t>
+          <t>-76.794902</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>316</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>314722</t>
+          <t>839065</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UNION</t>
+          <t>SAINT GERARD SCHOOL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.98809</t>
+          <t>-12.01429</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.83953</t>
+          <t>-76.93867</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>322</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>314736</t>
+          <t>585370</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>KOREB SCHOOL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.93823</t>
+          <t>-12.00595</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.69913</t>
+          <t>-76.87465</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>314755</t>
+          <t>104192</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>DEUNI</t>
+          <t>JESUS DE NAZARETH - BELEN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.9445</t>
+          <t>-11.98622</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.71089</t>
+          <t>-76.93539</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>314821</t>
+          <t>313789</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>EMANUEL</t>
+          <t>1282 AYMON LA CRUZ LOPEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.00365</t>
+          <t>-12.00228</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.92243</t>
+          <t>-76.92308</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>689</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>357764</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20955-2 NACIONES UNIDAS</t>
+          <t>LA CATOLICA DE CARAPONGO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.979292</t>
+          <t>-12.00418</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.910761</t>
+          <t>-76.87395</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>389</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>357783</t>
+          <t>314755</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20955-14 SAGRADO CORAZON DE JESUS</t>
+          <t>DEUNI</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.006905</t>
+          <t>-11.9445</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.956233</t>
+          <t>-76.71089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>357797</t>
+          <t>525164</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20955-17</t>
+          <t>WILLIAM SHAKESPEARE DE CARAPONGO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.985551</t>
+          <t>-12.00502</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.918991</t>
+          <t>-76.87543</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>320</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>357815</t>
+          <t>314661</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20955-18 JERUSALEN</t>
+          <t>SAN IISIDRO PATRON DE JICAMARCA / SAN ISIDRO PATRON DE JICAMARCA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.980042</t>
+          <t>-11.97697</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.831598</t>
+          <t>-76.94272</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>574</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>357858</t>
+          <t>314048</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CRISTO DE LA PAZ DE CAJAMARQUILLA</t>
+          <t>0058 CUSCO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.979027</t>
+          <t>-11.92888</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.908502</t>
+          <t>-76.69056</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>659</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>505180</t>
+          <t>718737</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20955-15</t>
+          <t>IDUKAY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.98342</t>
+          <t>-11.93442</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.929394</t>
+          <t>-76.68984</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>517338</t>
+          <t>804198</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PADRE MIGUEL MARINA</t>
+          <t>INTERNATIONAL COLLEGE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.9936</t>
+          <t>-11.97782</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.9545</t>
+          <t>-76.9387</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>525164</t>
+          <t>721792</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>WILLIAM SHAKESPEARE DE CARAPONGO</t>
+          <t>WINNER SCHOOL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.00502</t>
+          <t>-12.00382</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.87543</t>
+          <t>-76.9223</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>429</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>539236</t>
+          <t>314067</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>INMACULADA CORAZON DE MARIA</t>
+          <t>1198 LA RIBERA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.97685</t>
+          <t>-11.94326</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.9405</t>
+          <t>-76.70347</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>529</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>539298</t>
+          <t>722112</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1197 NICOLAS DE PIEROLA</t>
+          <t>CORAZON DE JESUS DE JICAMARCA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.94396</t>
+          <t>-11.9821</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-76.7122</t>
+          <t>-76.9341</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>902</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>572396</t>
+          <t>664857</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>COAR ARTISTICO DE LIMA / COLEGIO MAYOR SECUNDARIO PRESIDENTE DEL PERU</t>
+          <t>CORAZON DE JESUS DE JICAMARCA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.973926</t>
+          <t>-11.98225</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-76.773862</t>
+          <t>-76.934313</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>527</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>575069</t>
+          <t>313930</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LA CATOLICA DE CARAPONGO</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.00418</t>
+          <t>-11.9964</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.87395</t>
+          <t>-76.9226</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>872</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>585370</t>
+          <t>313713</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KOREB SCHOOL</t>
+          <t>0059 SANTA MARIA GORETTI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.00595</t>
+          <t>-11.98143</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-76.87465</t>
+          <t>-76.82186</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>965</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>619445</t>
+          <t>313708</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ANTONIO RAIMONDI</t>
+          <t>0055 MANUEL GONZALES PRADA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.98814</t>
+          <t>-11.93982</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-76.83947</t>
+          <t>-76.71179</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>691</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>651968</t>
+          <t>314576</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NUEVO MUNDO</t>
+          <t>LA ROCA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.96099</t>
+          <t>-11.94218</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-76.73794</t>
+          <t>-76.70663</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>232</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>664857</t>
+          <t>314227</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS DE JICAMARCA</t>
+          <t>JOSEFA CARRILLO Y ALBORNOZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-11.98225</t>
+          <t>-11.92845</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-76.934313</t>
+          <t>-76.68631</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>541</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>718426</t>
+          <t>314345</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0052 VIRGEN DE FATIMA</t>
+          <t>FOYER SANTA ROSA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.93779</t>
+          <t>-11.97814</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-76.69369</t>
+          <t>-76.81154</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>598</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>718737</t>
+          <t>314171</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>IDUKAY</t>
+          <t>PABLO PATRON</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.93442</t>
+          <t>-11.92764</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-76.68984</t>
+          <t>-76.68543</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>550</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>720325</t>
+          <t>357783</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN MARIA</t>
+          <t>20955-14 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-11.9899</t>
+          <t>-12.006905</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-76.91624</t>
+          <t>-76.956233</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>677</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>720410</t>
+          <t>314680</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PERUANO AMERICANO</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.0011</t>
+          <t>-11.93658</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-76.8771</t>
+          <t>-76.69814</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>491</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>720467</t>
+          <t>314289</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ANGELITOS DE JESUS</t>
+          <t>1277 DIVINO SALVADOR</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-11.993336</t>
+          <t>-11.9848</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-76.904096</t>
+          <t>-76.9486</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>720504</t>
+          <t>314604</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 58 MARY WARD</t>
+          <t>NUESTRA SEÑORA DE LA SABIDURIA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-11.969241</t>
+          <t>-11.9798</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-76.942479</t>
+          <t>-76.82</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>802</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>721792</t>
+          <t>505180</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>WINNER SCHOOL</t>
+          <t>20955-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.00382</t>
+          <t>-11.98342</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-76.9223</t>
+          <t>-76.929394</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>786</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>722112</t>
+          <t>720410</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS DE JICAMARCA</t>
+          <t>PERUANO AMERICANO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-11.9821</t>
+          <t>-12.0011</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-76.9341</t>
+          <t>-76.8771</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>735</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>737934</t>
+          <t>314519</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>20955-26 INMACULADA CONCEPCION</t>
+          <t>FE Y ALEGRIA 41</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.96624</t>
+          <t>-11.98122</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-76.794902</t>
+          <t>-76.83804</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,42 +5027,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>751208</t>
+          <t>314369</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KIDS &amp; KIDS</t>
+          <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.00564</t>
+          <t>-12.01796</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-76.92616</t>
+          <t>-76.94702</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>187</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5089,37 +5089,37 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>780098</t>
+          <t>807229</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SAN PEDRO Y SAN PABLO</t>
+          <t>FRANCOIS VIETE</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-11.96605</t>
+          <t>-12.001755</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-76.93461</t>
+          <t>-76.867586</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>187</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>800015</t>
+          <t>313727</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SEMILLITAS DEL VALLECITO IV</t>
+          <t>0033 VIRGILIO ESPINOZA BARRIOS</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-11.97257</t>
+          <t>-12.01372</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-76.83882</t>
+          <t>-76.91828</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>804198</t>
+          <t>720504</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>INTERNATIONAL COLLEGE</t>
+          <t>FE Y ALEGRIA 58 MARY WARD</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-11.97782</t>
+          <t>-11.969241</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-76.9387</t>
+          <t>-76.942479</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,37 +5275,37 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>807229</t>
+          <t>313591</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FRANCOIS VIETE</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.001755</t>
+          <t>-11.98169</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-76.867586</t>
+          <t>-76.91517</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>808059</t>
+          <t>314637</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>LITTLE LION OF JUDAH</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-11.9877</t>
+          <t>-11.93699</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-76.93417</t>
+          <t>-76.69467</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>814418</t>
+          <t>314213</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>REY SALOMON</t>
+          <t>1233 MANUEL FERNANDO CABREL NICHO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-11.97177</t>
+          <t>-11.9868</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-76.939611</t>
+          <t>-76.8989</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>823615</t>
+          <t>314722</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SAN PEDRO Y SAN PABLO</t>
+          <t>UNION</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.96436</t>
+          <t>-11.98809</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-76.93428</t>
+          <t>-76.83953</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,37 +5523,37 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>825600</t>
+          <t>357764</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CUSSI SCHOOL</t>
+          <t>20955-2 NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.002828</t>
+          <t>-11.979292</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-76.867478</t>
+          <t>-76.910761</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>835010</t>
+          <t>572396</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MONTESSORI DE CARAPONGO</t>
+          <t>COAR ARTISTICO DE LIMA / COLEGIO MAYOR SECUNDARIO PRESIDENTE DEL PERU</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.936429</t>
+          <t>-11.973926</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-76.696706</t>
+          <t>-76.773862</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>886</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>839046</t>
+          <t>314147</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ADELISES I</t>
+          <t>1205 ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-11.994589</t>
+          <t>-11.99263</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-76.941857</t>
+          <t>-76.91756</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>839065</t>
+          <t>314152</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAINT GERARD SCHOOL</t>
+          <t>0051 JOSE F. SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.01429</t>
+          <t>-11.99946</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-76.93867</t>
+          <t>-76.86647</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>854616</t>
+          <t>313652</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MASTER GENIO</t>
+          <t>COLEGIO EXPERIMENTAL DE APLICACION DE LA UNE ENRIQUE GUZMAN Y VALLE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.982406</t>
+          <t>-11.94414</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-76.941773</t>
+          <t>-76.69895</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>857040</t>
+          <t>313732</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>EL NAZARENO DE JESUS</t>
+          <t>1190 FELIPE HUAMAN POMA DE AYALA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.977326</t>
+          <t>-11.92475</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-76.937434</t>
+          <t>-76.68553</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>901444</t>
+          <t>313888</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>GOLEMAN SCHOOL</t>
+          <t>128 SANTA ROSITA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.975162</t>
+          <t>-11.98153</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-76.943886</t>
+          <t>-76.82217</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5929,6 +5929,254 @@
         </is>
       </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>150118</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>314086</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1197 NICOLAS DE PIEROLA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-11.94393</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-76.71215</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>150118</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>720467</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ANGELITOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-11.993336</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-76.904096</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>150118</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>800015</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SEMILLITAS DEL VALLECITO IV</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-11.97257</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-76.83882</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>150118</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>313845</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0027 SAN ANTONIO JICAMARCA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-11.98417</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-76.94085</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/LIMA-LIMA-LURIGANCHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LURIGANCHO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>755895</t>
+          <t>901444</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LAS BRISAS</t>
+          <t>GOLEMAN SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.99875</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.92141</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>-11.975162</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.943886</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>655235</t>
+          <t>857040</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE ÑAÑA</t>
+          <t>EL NAZARENO DE JESUS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.97709</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.80456</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>-11.977326</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.937434</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>655184</t>
+          <t>854616</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DIVINO NIÑO JESUS</t>
+          <t>MASTER GENIO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.97568</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.791</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>-11.982406</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.941773</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>619488</t>
+          <t>839065</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LOS ALAMOS</t>
+          <t>SAINT GERARD SCHOOL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.98655</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.83315</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>-12.01429</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.93867</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>313685</t>
+          <t>839046</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>200 LOS ANGELITOS DEL SABER</t>
+          <t>ADELISES I</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.0014</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.8835</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>-11.994589</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.941857</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>357815</t>
+          <t>835010</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20955-18 JERUSALEN</t>
+          <t>MONTESSORI DE CARAPONGO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.980042</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.831598</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-11.936429</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.696706</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,42 +873,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>539236</t>
+          <t>825600</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>INMACULADA CORAZON DE MARIA</t>
+          <t>CUSSI SCHOOL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.97685</t>
+          <t>191</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.9405</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-12.002828</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.867478</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -945,22 +945,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>-11.96436</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>-76.93428</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,42 +997,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>825600</t>
+          <t>814418</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CUSSI SCHOOL</t>
+          <t>REY SALOMON</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.002828</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.867478</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>-11.97177</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.939611</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>313954</t>
+          <t>808059</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>LITTLE LION OF JUDAH</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.99909</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.86713</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-11.9877</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.93417</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>517338</t>
+          <t>807229</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PADRE MIGUEL MARINA</t>
+          <t>FRANCOIS VIETE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.9936</t>
+          <t>187</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.9545</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>-12.001755</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.867586</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>780098</t>
+          <t>804198</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN PEDRO Y SAN PABLO</t>
+          <t>INTERNATIONAL COLLEGE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.96605</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.93461</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>-11.97782</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.9387</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>839046</t>
+          <t>800015</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ADELISES I</t>
+          <t>SEMILLITAS DEL VALLECITO IV</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.994589</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.941857</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-11.97257</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.83882</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,42 +1307,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>313874</t>
+          <t>780098</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>SAN PEDRO Y SAN PABLO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.0192</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.91942</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>-11.96605</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.93461</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>314246</t>
+          <t>755895</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>LAS BRISAS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.98006</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.90824</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>-11.99875</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.92141</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>314251</t>
+          <t>751208</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>KIDS &amp; KIDS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.00154</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.93246</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>-12.00564</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.92616</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>718426</t>
+          <t>737934</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0052 VIRGEN DE FATIMA</t>
+          <t>20955-26 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.93779</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.69369</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>-11.96624</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.794902</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>313850</t>
+          <t>722112</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1234 / 1234 ROSA SANTANA PISCONTE</t>
+          <t>CORAZON DE JESUS DE JICAMARCA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.93427</t>
+          <t>902</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.71576</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-11.9821</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.9341</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>314034</t>
+          <t>721792</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>WINNER SCHOOL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.93454</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.69095</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>-12.00382</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.9223</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>314053</t>
+          <t>720504</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0063 LETICIA KIEFFER MARCHAND</t>
+          <t>FE Y ALEGRIA 58 MARY WARD</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.93872</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.69901</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-11.969241</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.942479</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>619445</t>
+          <t>720467</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ANTONIO RAIMONDI</t>
+          <t>ANGELITOS DE JESUS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.98814</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.83947</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>-11.993336</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.904096</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>751208</t>
+          <t>720410</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KIDS &amp; KIDS</t>
+          <t>PERUANO AMERICANO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.00564</t>
+          <t>735</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.92616</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-12.0011</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.8771</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>814418</t>
+          <t>720325</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>REY SALOMON</t>
+          <t>SANTISIMA VIRGEN MARIA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.97177</t>
+          <t>335</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.939611</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-11.9899</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.91624</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>901444</t>
+          <t>718737</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GOLEMAN SCHOOL</t>
+          <t>IDUKAY</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.975162</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.943886</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>-11.93442</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.68984</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>313794</t>
+          <t>718426</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1206 DANIEL ALCIDES CARRION</t>
+          <t>0052 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.94819</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.7298</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>-11.93779</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.69369</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>720325</t>
+          <t>664857</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SANTISIMA VIRGEN MARIA</t>
+          <t>CORAZON DE JESUS DE JICAMARCA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.9899</t>
+          <t>527</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.91624</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>-11.98225</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.934313</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>857040</t>
+          <t>655235</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>EL NAZARENO DE JESUS</t>
+          <t>SAN IGNACIO DE ÑAÑA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.977326</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.937434</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-11.97709</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.80456</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>313628</t>
+          <t>655184</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.98381</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.94133</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>-11.97568</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.791</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>314005</t>
+          <t>651968</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>NUEVO MUNDO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.99723</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.91196</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-11.96099</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.73794</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>808059</t>
+          <t>619488</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LITTLE LION OF JUDAH</t>
+          <t>LOS ALAMOS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.9877</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.93417</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-11.98655</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.83315</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>835010</t>
+          <t>619445</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MONTESSORI DE CARAPONGO</t>
+          <t>ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.936429</t>
+          <t>253</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.696706</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-11.98814</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.83947</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>314581</t>
+          <t>585370</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MI JESUS</t>
+          <t>KOREB SCHOOL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.98328</t>
+          <t>335</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.83671</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-12.00595</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.87465</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>357797</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20955-17</t>
+          <t>LA CATOLICA DE CARAPONGO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.985551</t>
+          <t>389</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.918991</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>-12.00418</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.87395</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>854616</t>
+          <t>572396</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MASTER GENIO</t>
+          <t>COAR ARTISTICO DE LIMA / COLEGIO MAYOR SECUNDARIO PRESIDENTE DEL PERU</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.982406</t>
+          <t>886</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.941773</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-11.973926</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.773862</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>313911</t>
+          <t>539298</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1195 CESAR VALLEJO</t>
+          <t>1197 NICOLAS DE PIEROLA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.94207</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.69933</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>-11.94396</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.7122</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>314114</t>
+          <t>539236</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1200 SANTA MARIA</t>
+          <t>INMACULADA CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.948573</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.716791</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-11.97685</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.9405</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>314821</t>
+          <t>525164</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EMANUEL</t>
+          <t>WILLIAM SHAKESPEARE DE CARAPONGO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.00365</t>
+          <t>320</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.92243</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-12.00502</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.87543</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>651968</t>
+          <t>517338</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NUEVO MUNDO</t>
+          <t>PADRE MIGUEL MARINA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.96099</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.73794</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>-11.9936</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.9545</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>313633</t>
+          <t>505180</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>20955-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.9717</t>
+          <t>786</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.8961</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>-11.98342</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.929394</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>313765</t>
+          <t>357858</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0065 MARISCAL ANDRES A. CACERES</t>
+          <t>CRISTO DE LA PAZ DE CAJAMARQUILLA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.9336</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.70291</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-11.979027</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.908502</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>314736</t>
+          <t>357815</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>20955-18 JERUSALEN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.93823</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.69913</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>-11.980042</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.831598</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>357858</t>
+          <t>357797</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CRISTO DE LA PAZ DE CAJAMARQUILLA</t>
+          <t>20955-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.979027</t>
+          <t>339</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.908502</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-11.985551</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.918991</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>539298</t>
+          <t>357783</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1197 NICOLAS DE PIEROLA</t>
+          <t>20955-14 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.94396</t>
+          <t>677</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.7122</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>-12.006905</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.956233</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>737934</t>
+          <t>357764</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20955-26 INMACULADA CONCEPCION</t>
+          <t>20955-2 NACIONES UNIDAS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.96624</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.794902</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>-11.979292</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.910761</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>839065</t>
+          <t>314821</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAINT GERARD SCHOOL</t>
+          <t>EMANUEL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.01429</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.93867</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>-12.00365</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.92243</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>585370</t>
+          <t>314755</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KOREB SCHOOL</t>
+          <t>DEUNI</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.00595</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.87465</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>-11.9445</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.71089</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>104192</t>
+          <t>314736</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARETH - BELEN</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.98622</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.93539</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-11.93823</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.69913</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>313789</t>
+          <t>314722</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1282 AYMON LA CRUZ LOPEZ</t>
+          <t>UNION</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.00228</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.92308</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>-11.98809</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.83953</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>575069</t>
+          <t>314680</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LA CATOLICA DE CARAPONGO</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.00418</t>
+          <t>491</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.87395</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>-11.93658</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.69814</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>314755</t>
+          <t>314661</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DEUNI</t>
+          <t>SAN IISIDRO PATRON DE JICAMARCA / SAN ISIDRO PATRON DE JICAMARCA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.9445</t>
+          <t>574</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.71089</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-11.97697</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.94272</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>525164</t>
+          <t>314637</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WILLIAM SHAKESPEARE DE CARAPONGO</t>
+          <t>SAN ISIDRO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.00502</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.87543</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>-11.93699</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.69467</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>314661</t>
+          <t>314604</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SAN IISIDRO PATRON DE JICAMARCA / SAN ISIDRO PATRON DE JICAMARCA</t>
+          <t>NUESTRA SEÑORA DE LA SABIDURIA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.97697</t>
+          <t>802</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.94272</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>-11.9798</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.82</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>314048</t>
+          <t>314581</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0058 CUSCO</t>
+          <t>MI JESUS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.92888</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.69056</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>-11.98328</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.83671</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>718737</t>
+          <t>314576</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IDUKAY</t>
+          <t>LA ROCA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.93442</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.68984</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-11.94218</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.70663</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>804198</t>
+          <t>314519</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>INTERNATIONAL COLLEGE</t>
+          <t>FE Y ALEGRIA 41</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.97782</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.9387</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-11.98122</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.83804</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,37 +3911,37 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>721792</t>
+          <t>314369</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>WINNER SCHOOL</t>
+          <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.00382</t>
+          <t>187</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.9223</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>-12.01796</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-76.94702</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>314067</t>
+          <t>314345</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1198 LA RIBERA</t>
+          <t>FOYER SANTA ROSA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.94326</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.70347</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>-11.97814</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.81154</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>722112</t>
+          <t>314289</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS DE JICAMARCA</t>
+          <t>1277 DIVINO SALVADOR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.9821</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-76.9341</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>-11.9848</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.9486</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>664857</t>
+          <t>314251</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS DE JICAMARCA</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.98225</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-76.934313</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>-12.00154</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-76.93246</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>313930</t>
+          <t>314246</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.9964</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.9226</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>-11.98006</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.90824</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>313713</t>
+          <t>314227</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0059 SANTA MARIA GORETTI</t>
+          <t>JOSEFA CARRILLO Y ALBORNOZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-11.98143</t>
+          <t>541</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-76.82186</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>-11.92845</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-76.68631</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>313708</t>
+          <t>314213</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0055 MANUEL GONZALES PRADA</t>
+          <t>1233 MANUEL FERNANDO CABREL NICHO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.93982</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-76.71179</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>-11.9868</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-76.8989</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>314576</t>
+          <t>314171</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LA ROCA</t>
+          <t>PABLO PATRON</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.94218</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-76.70663</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>-11.92764</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.68543</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>314227</t>
+          <t>314152</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JOSEFA CARRILLO Y ALBORNOZ</t>
+          <t>0051 JOSE F. SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-11.92845</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-76.68631</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>-11.99946</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.86647</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>314345</t>
+          <t>314147</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FOYER SANTA ROSA</t>
+          <t>1205 ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.97814</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-76.81154</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>-11.99263</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.91756</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>314171</t>
+          <t>314114</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PABLO PATRON</t>
+          <t>1200 SANTA MARIA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.92764</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-76.68543</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>-11.948573</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-76.716791</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>357783</t>
+          <t>314086</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20955-14 SAGRADO CORAZON DE JESUS</t>
+          <t>1197 NICOLAS DE PIEROLA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.006905</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-76.956233</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>-11.94393</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-76.71215</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>314680</t>
+          <t>314067</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>1198 LA RIBERA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-11.93658</t>
+          <t>529</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-76.69814</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>-11.94326</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-76.70347</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>314289</t>
+          <t>314053</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1277 DIVINO SALVADOR</t>
+          <t>0063 LETICIA KIEFFER MARCHAND</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-11.9848</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-76.9486</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>-11.93872</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-76.69901</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>314604</t>
+          <t>314048</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA SABIDURIA</t>
+          <t>0058 CUSCO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-11.9798</t>
+          <t>659</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-76.82</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>-11.92888</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-76.69056</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>505180</t>
+          <t>314034</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20955-15</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-11.98342</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-76.929394</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>-11.93454</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-76.69095</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>720410</t>
+          <t>314005</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PERUANO AMERICANO</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.0011</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-76.8771</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>-11.99723</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-76.91196</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>314519</t>
+          <t>313954</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 41</t>
+          <t>161</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.98122</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-76.83804</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>-11.99909</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-76.86713</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,42 +5027,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>314369</t>
+          <t>313930</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SANTA RITA DE CASIA</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.01796</t>
+          <t>872</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-76.94702</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>-11.9964</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.9226</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5089,42 +5089,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>807229</t>
+          <t>313911</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FRANCOIS VIETE</t>
+          <t>1195 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.001755</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-76.867586</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>-11.94207</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.69933</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>313727</t>
+          <t>313888</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0033 VIRGILIO ESPINOZA BARRIOS</t>
+          <t>128 SANTA ROSITA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.01372</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-76.91828</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>-11.98153</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-76.82217</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5213,42 +5213,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>720504</t>
+          <t>313874</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 58 MARY WARD</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-11.969241</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-76.942479</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>-12.0192</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-76.91942</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>313591</t>
+          <t>313850</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1234 / 1234 ROSA SANTANA PISCONTE</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-11.98169</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-76.91517</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>-11.93427</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-76.71576</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>314637</t>
+          <t>313845</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAN ISIDRO</t>
+          <t>0027 SAN ANTONIO JICAMARCA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-11.93699</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-76.69467</t>
+          <t>95</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-11.98417</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-76.94085</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>314213</t>
+          <t>313794</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1233 MANUEL FERNANDO CABREL NICHO</t>
+          <t>1206 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-11.9868</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-76.8989</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>-11.94819</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-76.7298</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>314722</t>
+          <t>313789</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>UNION</t>
+          <t>1282 AYMON LA CRUZ LOPEZ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.98809</t>
+          <t>689</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-76.83953</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>-12.00228</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-76.92308</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>357764</t>
+          <t>313765</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20955-2 NACIONES UNIDAS</t>
+          <t>0065 MARISCAL ANDRES A. CACERES</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.979292</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-76.910761</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>-11.9336</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-76.70291</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>572396</t>
+          <t>313732</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>COAR ARTISTICO DE LIMA / COLEGIO MAYOR SECUNDARIO PRESIDENTE DEL PERU</t>
+          <t>1190 FELIPE HUAMAN POMA DE AYALA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.973926</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-76.773862</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>-11.92475</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-76.68553</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>314147</t>
+          <t>313727</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1205 ABELARDO QUIÑONES</t>
+          <t>0033 VIRGILIO ESPINOZA BARRIOS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-11.99263</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-76.91756</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-12.01372</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.91828</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>314152</t>
+          <t>313713</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0051 JOSE F. SANCHEZ CARRION</t>
+          <t>0059 SANTA MARIA GORETTI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-11.99946</t>
+          <t>965</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-76.86647</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>-11.98143</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-76.82186</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>313652</t>
+          <t>313708</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>COLEGIO EXPERIMENTAL DE APLICACION DE LA UNE ENRIQUE GUZMAN Y VALLE</t>
+          <t>0055 MANUEL GONZALES PRADA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.94414</t>
+          <t>691</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-76.69895</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>-11.93982</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-76.71179</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,37 +5833,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>313732</t>
+          <t>313685</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1190 FELIPE HUAMAN POMA DE AYALA</t>
+          <t>200 LOS ANGELITOS DEL SABER</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.92475</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-76.68553</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>-12.0014</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-76.8835</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>313888</t>
+          <t>313652</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>128 SANTA ROSITA</t>
+          <t>COLEGIO EXPERIMENTAL DE APLICACION DE LA UNE ENRIQUE GUZMAN Y VALLE</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.98153</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-76.82217</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-11.94414</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.69895</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>314086</t>
+          <t>313633</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1197 NICOLAS DE PIEROLA</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-11.94393</t>
+          <t>504</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-76.71215</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-11.9717</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.8961</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>720467</t>
+          <t>313628</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ANGELITOS DE JESUS</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-11.993336</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-76.904096</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>-11.98381</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.94133</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>800015</t>
+          <t>313591</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SEMILLITAS DEL VALLECITO IV</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-11.97257</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-76.83882</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-11.98169</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.91517</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>313845</t>
+          <t>104192</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0027 SAN ANTONIO JICAMARCA</t>
+          <t>JESUS DE NAZARETH - BELEN</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.98417</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-76.94085</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>-11.98622</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>-76.93539</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-LURIGANCHO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LURIGANCHO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
